--- a/skills/code/自制/aDNA-downloader/template/古代DNA收集模板-AI-agent.xlsx
+++ b/skills/code/自制/aDNA-downloader/template/古代DNA收集模板-AI-agent.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f9b67a23c0eaa71/文档（共享）/4_古代DNA/1-古代DNA数据下载和信息收集-AI-agent/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{169481FB-FAA5-4AD8-A99F-DC111628729E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6A286688-2AD7-4EEF-A5C9-DC726B88A6FE}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{169481FB-FAA5-4AD8-A99F-DC111628729E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AF4338A-5096-4AF7-8FB5-5884C75791A7}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="8316" yWindow="4236" windowWidth="14580" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="252" windowWidth="30936" windowHeight="17136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
-    <sheet name="GnecchiRuscone_Nature_2024" sheetId="2" r:id="rId2"/>
+    <sheet name="作者_期刊_年份" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -359,10 +359,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>必填；原始数据类型：FASTQ,BAM,FASTA,VCF,Table,Other,Unkown</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>BAM</t>
   </si>
   <si>
@@ -402,10 +398,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>必填；死亡年龄；文本；可填 Adult/Juvenile/数值范围；未知则填Unkown</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>必填；线粒体单倍群；文本；缺失填 Unknown</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -415,18 +407,6 @@
   </si>
   <si>
     <t>必填；下拉；单倍群来源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>必填；整数；BP 年代中心值；未知则填Unkown</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>必填；整数；BP 区间下限；未知则填Unkown</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>必填；整数；BP 区间上限；未知则填Unkown</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -466,16 +446,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>必填；生业模式标签；统一后用于筛选；格式：地区_生业模式_时期；例如：East_Asia_Yellow_River_Millet_Agriculture_Neolithic，East_Asia_Yangtze_River_Rice_Agriculture_Neolithic，
-West_Asia_Wheat_Barley_Agriculture_Neolithic，
-South_Asia_Mixed_Agriculture_Bronze_Age，
-Central_Asia_Nomadic_Pastoralism_Iron_Age，
-Oceania_Tropical_Horticulture_Late_Holocene，
-North_America_Maize_Agriculture_Late_Woodland，
-South_America_Tuber_Agriculture_Formative……</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>必填；论文 DOI；文本；缺失填 Unknown</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -502,6 +472,31 @@
   <si>
     <t>Citation_short</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填；禁止填Unknown；必须按照如下格式：大洲_地区_生业模式_时期；例如：East_Asia_Yellow_River_Millet_Agriculture_Neolithic，East_Asia_Yangtze_River_Rice_Agriculture_Neolithic，
+West_Asia_Wheat_Barley_Agriculture_Neolithic，
+South_Asia_Mixed_Agriculture_Bronze_Age，
+Central_Asia_Nomadic_Pastoralism_Iron_Age，
+Oceania_Tropical_Horticulture_Late_Holocene，
+North_America_Maize_Agriculture_Late_Woodland，
+South_America_Tuber_Agriculture_Formative……</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填；原始数据类型：FASTQ,BAM,FASTA,VCF,Table,Other,Unknown</t>
+  </si>
+  <si>
+    <t>必填；死亡年龄；文本；可填 Adult/Juvenile/数值范围；未知则填Unknown</t>
+  </si>
+  <si>
+    <t>必填；整数；BP 年代中心值；未知则填Unknown</t>
+  </si>
+  <si>
+    <t>必填；整数；BP 区间下限；未知则填Unknown</t>
+  </si>
+  <si>
+    <t>必填；整数；BP 区间上限；未知则填Unknown</t>
   </si>
 </sst>
 </file>
@@ -932,7 +927,7 @@
         <v>27</v>
       </c>
       <c r="AJ1" s="6" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="AK1" s="6" t="s">
         <v>28</v>
@@ -949,7 +944,7 @@
         <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>38</v>
@@ -958,7 +953,7 @@
         <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>39</v>
@@ -967,67 +962,67 @@
         <v>47</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="R2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="V2" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="Q2" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="R2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>111</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="X2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="AC2" s="3" t="s">
         <v>56</v>
@@ -1036,31 +1031,31 @@
         <v>57</v>
       </c>
       <c r="AE2" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="AH2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="AJ2" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AK2" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AL2" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="AG2" s="3" t="s">
+      <c r="AM2" s="14" t="s">
         <v>123</v>
-      </c>
-      <c r="AH2" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="AI2" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ2" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK2" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="AL2" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="AM2" s="14" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:39" ht="15" customHeight="1">
@@ -1068,7 +1063,7 @@
         <v>78</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>80</v>
@@ -1187,7 +1182,7 @@
         <v>77</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>79</v>
@@ -1223,10 +1218,10 @@
         <v>60</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P4" s="5" t="s">
         <v>85</v>

--- a/skills/code/自制/aDNA-downloader/template/古代DNA收集模板-AI-agent.xlsx
+++ b/skills/code/自制/aDNA-downloader/template/古代DNA收集模板-AI-agent.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7f9b67a23c0eaa71/文档（共享）/4_古代DNA/1-古代DNA数据下载和信息收集-AI-agent/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{169481FB-FAA5-4AD8-A99F-DC111628729E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AF4338A-5096-4AF7-8FB5-5884C75791A7}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{169481FB-FAA5-4AD8-A99F-DC111628729E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{553A6A9D-E755-4AE9-9D47-8884BD4F892F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="252" windowWidth="30936" windowHeight="17136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="134">
   <si>
     <t>Run_accession</t>
   </si>
@@ -490,13 +490,28 @@
     <t>必填；死亡年龄；文本；可填 Adult/Juvenile/数值范围；未知则填Unknown</t>
   </si>
   <si>
-    <t>必填；整数；BP 年代中心值；未知则填Unknown</t>
+    <t>Genetic_marker</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>必填；整数；BP 区间下限；未知则填Unknown</t>
+    <t>必填；遗传标记类型；仅能选择填写如下内容：nDNA (include chrY+mtDNA),chrY,mtDNA,mtDNA+chrY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>必填；整数；BP 区间上限；未知则填Unknown</t>
+    <t>nDNA (include chrY+mtDNA)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填；整数；BP 年代中心值；若文献未提供精确时间，则根据文献大致推断时间并加问号例如5000?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填；整数；BP 区间下限；若文献未提供精确时间，则根据文献大致推断时间并加问号例如4500?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必填；整数；BP 区间上限；若文献未提供精确时间，则根据文献大致推断时间并加问号例如5500?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -564,7 +579,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -610,6 +625,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -780,7 +798,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AM1157"/>
+  <dimension ref="A1:AN1157"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="22.59765625" style="18" customWidth="1"/>
@@ -817,10 +835,11 @@
     <col min="37" max="37" width="67.59765625" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="10.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="17.8984375" style="16" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="8.796875" style="1"/>
+    <col min="40" max="40" width="26.59765625" style="1" customWidth="1"/>
+    <col min="41" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="4" customFormat="1" ht="15" customHeight="1">
+    <row r="1" spans="1:40" s="4" customFormat="1" ht="15" customHeight="1">
       <c r="A1" s="11" t="s">
         <v>41</v>
       </c>
@@ -938,8 +957,11 @@
       <c r="AM1" s="13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:39" s="8" customFormat="1" ht="57.6" customHeight="1">
+      <c r="AN1" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40" s="8" customFormat="1" ht="77.400000000000006" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>40</v>
       </c>
@@ -992,13 +1014,13 @@
         <v>108</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="U2" s="3" t="s">
         <v>110</v>
@@ -1057,8 +1079,11 @@
       <c r="AM2" s="14" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="3" spans="1:39" ht="15" customHeight="1">
+      <c r="AN2" s="19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40" ht="15" customHeight="1">
       <c r="A3" s="17" t="s">
         <v>78</v>
       </c>
@@ -1176,8 +1201,11 @@
       <c r="AM3" s="15">
         <v>2024</v>
       </c>
-    </row>
-    <row r="4" spans="1:39" ht="15" customHeight="1">
+      <c r="AN3" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" ht="15" customHeight="1">
       <c r="A4" s="17" t="s">
         <v>77</v>
       </c>
@@ -1295,8 +1323,11 @@
       <c r="AM4" s="15">
         <v>2024</v>
       </c>
-    </row>
-    <row r="5" spans="1:39" ht="15" customHeight="1">
+      <c r="AN4" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40" ht="15" customHeight="1">
       <c r="A5" s="17"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1337,7 +1368,7 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="15"/>
     </row>
-    <row r="6" spans="1:39" ht="15" customHeight="1">
+    <row r="6" spans="1:40" ht="15" customHeight="1">
       <c r="A6" s="17"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1378,7 +1409,7 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="15"/>
     </row>
-    <row r="7" spans="1:39" ht="15" customHeight="1">
+    <row r="7" spans="1:40" ht="15" customHeight="1">
       <c r="A7" s="17"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -1419,7 +1450,7 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="15"/>
     </row>
-    <row r="8" spans="1:39" ht="15" customHeight="1">
+    <row r="8" spans="1:40" ht="15" customHeight="1">
       <c r="A8" s="17"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -1460,7 +1491,7 @@
       <c r="AL8" s="5"/>
       <c r="AM8" s="15"/>
     </row>
-    <row r="9" spans="1:39" ht="15" customHeight="1">
+    <row r="9" spans="1:40" ht="15" customHeight="1">
       <c r="A9" s="17"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1501,7 +1532,7 @@
       <c r="AL9" s="5"/>
       <c r="AM9" s="15"/>
     </row>
-    <row r="10" spans="1:39" ht="15" customHeight="1">
+    <row r="10" spans="1:40" ht="15" customHeight="1">
       <c r="A10" s="17"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1542,7 +1573,7 @@
       <c r="AL10" s="5"/>
       <c r="AM10" s="15"/>
     </row>
-    <row r="11" spans="1:39" ht="15" customHeight="1">
+    <row r="11" spans="1:40" ht="15" customHeight="1">
       <c r="A11" s="17"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1583,7 +1614,7 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="15"/>
     </row>
-    <row r="12" spans="1:39" ht="15" customHeight="1">
+    <row r="12" spans="1:40" ht="15" customHeight="1">
       <c r="A12" s="17"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1624,7 +1655,7 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="15"/>
     </row>
-    <row r="13" spans="1:39" ht="15" customHeight="1">
+    <row r="13" spans="1:40" ht="15" customHeight="1">
       <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1665,7 +1696,7 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="15"/>
     </row>
-    <row r="14" spans="1:39" ht="15" customHeight="1">
+    <row r="14" spans="1:40" ht="15" customHeight="1">
       <c r="A14" s="17"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1706,7 +1737,7 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="15"/>
     </row>
-    <row r="15" spans="1:39" ht="15" customHeight="1">
+    <row r="15" spans="1:40" ht="15" customHeight="1">
       <c r="A15" s="17"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1747,7 +1778,7 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="15"/>
     </row>
-    <row r="16" spans="1:39" ht="15" customHeight="1">
+    <row r="16" spans="1:40" ht="15" customHeight="1">
       <c r="A16" s="17"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -42845,7 +42876,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="10">
+  <dataValidations count="11">
     <dataValidation type="list" sqref="K3:K998" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Female,Male,Unknown"</formula1>
     </dataValidation>
@@ -42877,6 +42908,9 @@
       <formula1>1000</formula1>
       <formula2>3000</formula2>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN3:AN1151" xr:uid="{2ABD2372-B7FD-445C-A8F3-51AAC7297815}">
+      <formula1>"nDNA (include chrY+mtDNA),chrY,mtDNA,mtDNA+chrY"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
